--- a/Torpedo test.xlsx
+++ b/Torpedo test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Balázs\SzofTech\lab4\se-lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{973244FB-5DFD-47F0-926C-DF050A988842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87089E68-5377-4685-9CDF-F8D432BDA3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D909D3C0-7051-47AE-97C6-BBA3A89C18F1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D909D3C0-7051-47AE-97C6-BBA3A89C18F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Teszt követelmény</t>
   </si>
@@ -83,9 +83,6 @@
     <t>SUCCESS, SUCCESS</t>
   </si>
   <si>
-    <t>SUCCESS, FAILURE</t>
-  </si>
-  <si>
     <t>Elvárt kimenet</t>
   </si>
   <si>
@@ -93,6 +90,12 @@
   </si>
   <si>
     <t>Előfeltétel</t>
+  </si>
+  <si>
+    <t>SUCCESS, FAIL</t>
+  </si>
+  <si>
+    <t>SUCCESS,FAIL</t>
   </si>
 </sst>
 </file>
@@ -490,13 +493,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -524,7 +527,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -538,7 +541,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -552,7 +555,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -566,7 +569,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -594,7 +597,7 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
